--- a/Outputs/Scenarios/PtX_demand_CZ_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CZ_Electrification.xlsx
@@ -507,7 +507,7 @@
         <v>0.01133895372074527</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0078867012569355</v>
+        <v>0.007886701256935502</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -516,7 +516,7 @@
         <v>0.004105922140507</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0028430581042284</v>
+        <v>0.002843058104228399</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>6.17253291988699e-07</v>
+        <v>6.172532919886989e-07</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.469013167954796e-06</v>
+        <v>2.469013167954795e-06</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0002402216393152396</v>
       </c>
       <c r="K42" t="n">
-        <v>6.17253291988699e-07</v>
+        <v>6.172532919886989e-07</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_CZ_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_CZ_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.003083138472135582</v>
       </c>
       <c r="K16" t="n">
-        <v>6.781130811114477e-07</v>
+        <v>1.553399324654981e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.13018846851908e-07</v>
+        <v>6.65742567709278e-08</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.520753874076318e-07</v>
+        <v>2.662970270837112e-07</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6.781130811114477e-07</v>
+        <v>2.662970270837112e-07</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0002470832921338098</v>
       </c>
       <c r="K24" t="n">
-        <v>1.243088022544233e-06</v>
+        <v>1.22041092417923e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.001495595687104884</v>
       </c>
       <c r="K25" t="n">
-        <v>8.887218591023915e-06</v>
+        <v>8.725093040359002e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>4.442280650532449e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>1.13018846851908e-07</v>
+        <v>6.65742567709278e-08</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.004564211146989551</v>
       </c>
       <c r="K30" t="n">
-        <v>3.703519751932193e-06</v>
+        <v>7.777391479057606e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>6.172532919886989e-07</v>
+        <v>3.333167776738975e-07</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.469013167954795e-06</v>
+        <v>1.33326711069559e-06</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.703519751932193e-06</v>
+        <v>1.33326711069559e-06</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0002402216393152396</v>
       </c>
       <c r="K42" t="n">
-        <v>6.172532919886989e-07</v>
+        <v>3.333167776738975e-07</v>
       </c>
     </row>
     <row r="43">
